--- a/Aula12/cadastro_alunos.xlsx
+++ b/Aula12/cadastro_alunos.xlsx
@@ -439,10 +439,8 @@
           <t>Iara</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+      <c r="B2" t="n">
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>160</v>
